--- a/Docs/UART_Verification_Plan.xlsx
+++ b/Docs/UART_Verification_Plan.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Verification\UART\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Verification\UART\UART_Verification\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51C3A065-E338-44D9-A98C-DF94D279399D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F95DE61-A472-499A-8E0A-38E8FB3885A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BF644B0F-BA16-4817-B411-9FABE2A9FBC0}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="38">
   <si>
     <t>Checker</t>
   </si>
@@ -74,23 +74,100 @@
     <t>Verify That</t>
   </si>
   <si>
-    <t xml:space="preserve">1- check the data is received correctly 
+    <t>Constraints</t>
+  </si>
+  <si>
+    <t>Prescale must be 4,8,16 or 32</t>
+  </si>
+  <si>
+    <t>cover group</t>
+  </si>
+  <si>
+    <t>cover point</t>
+  </si>
+  <si>
+    <t>coverpoint description</t>
+  </si>
+  <si>
+    <t>no. of bins</t>
+  </si>
+  <si>
+    <t>reset</t>
+  </si>
+  <si>
+    <t>Covers the reset signal (rx_item.rst)
+transitions and states</t>
+  </si>
+  <si>
+    <t>par_en</t>
+  </si>
+  <si>
+    <t>Covers the parity enable signal
+(rx_item.par_en) states.</t>
+  </si>
+  <si>
+    <t>rx_cvg</t>
+  </si>
+  <si>
+    <t>par_type</t>
+  </si>
+  <si>
+    <t>overs the parity type signal (rx_item.par_type) states.</t>
+  </si>
+  <si>
+    <t>prescale</t>
+  </si>
+  <si>
+    <t>Covers the prescale value (rx_item.prescale) states.</t>
+  </si>
+  <si>
+    <t>Valid_checking</t>
+  </si>
+  <si>
+    <t>Covers the RX output valid signal 
+(rx_item.RX_out_valid) states</t>
+  </si>
+  <si>
+    <t>cross2</t>
+  </si>
+  <si>
+    <t>Covers the cross between par_en and par_type</t>
+  </si>
+  <si>
+    <t>In whch transaction</t>
+  </si>
+  <si>
+    <t>RX_Transaction</t>
+  </si>
+  <si>
+    <t>1- check the data is received correctly 
 after 11/10 clock cycles 
-2- check the Busy is asserted one clock cycle after the Valid is rased
-3- check the parity </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1- check the Parallel data is received correctly 
+2- check the Busy is asserted one clock cycle 
+after the Valid is rased
+3- check the parity</t>
+  </si>
+  <si>
+    <t>1- check the Parallel data is received correctly 
 after 11/10 clock cycles of the transmitter clock
-2- check the Valid is asserted in the 12th/11th clock cycle of the transmitter clock
-3- check the parity </t>
+2- check the Valid is asserted in the 12th/11th
+clock cycle of the transmitter clock
+3- check the parity</t>
+  </si>
+  <si>
+    <t>RX RX Features</t>
+  </si>
+  <si>
+    <t>Error Injection, Incorrect strart/stop bits</t>
+  </si>
+  <si>
+    <t>Check the valid flag</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -105,8 +182,32 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFF1A983"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -121,24 +222,48 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor rgb="FF9FC5E8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
+        <fgColor rgb="FFD9EAD3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
+        <fgColor rgb="FFF9CB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAF2D0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA6C9EC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1A983"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -146,106 +271,71 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
-      <bottom style="thin">
-        <color theme="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -581,148 +671,324 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{833C06F7-1151-4F32-BC64-8EC40EE31342}">
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.88671875" customWidth="1"/>
     <col min="2" max="2" width="38.33203125" customWidth="1"/>
-    <col min="3" max="3" width="40.33203125" customWidth="1"/>
+    <col min="3" max="3" width="44.77734375" customWidth="1"/>
     <col min="4" max="4" width="31.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="2"/>
-      <c r="B1" s="4" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="5"/>
+      <c r="B1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2"/>
-      <c r="B2" s="7" t="s">
+      <c r="E1" s="7"/>
+    </row>
+    <row r="2" spans="1:6" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="5"/>
+      <c r="B2" s="8" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+    </row>
+    <row r="3" spans="1:6" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="9"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="7"/>
+    </row>
+    <row r="4" spans="1:6" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5"/>
+      <c r="B4" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="9"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+    </row>
+    <row r="5" spans="1:6" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5"/>
+      <c r="B5" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+    </row>
+    <row r="6" spans="1:6" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="12"/>
+      <c r="B6" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="12"/>
+      <c r="B7" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="9"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="9"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="12"/>
+      <c r="B10" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="12"/>
+      <c r="B11" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="7"/>
+    </row>
+    <row r="15" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A15" s="17"/>
+      <c r="B15" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="15">
+        <v>4</v>
+      </c>
+      <c r="E15" s="7"/>
+    </row>
+    <row r="16" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A16" s="17"/>
+      <c r="B16" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="15">
+        <v>2</v>
+      </c>
+      <c r="E16" s="7"/>
+      <c r="F16" s="4"/>
+    </row>
+    <row r="17" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A17" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="15">
+        <v>2</v>
+      </c>
+      <c r="E17" s="7"/>
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A18" s="17"/>
+      <c r="B18" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" s="15">
+        <v>4</v>
+      </c>
+      <c r="E18" s="7"/>
+      <c r="F18" s="4"/>
+    </row>
+    <row r="19" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A19" s="17"/>
+      <c r="B19" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="15">
+        <v>2</v>
+      </c>
+      <c r="E19" s="7"/>
+      <c r="F19" s="4"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="17"/>
+      <c r="B20" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" s="15">
+        <v>4</v>
+      </c>
+      <c r="E20" s="7"/>
+      <c r="F20" s="4"/>
+    </row>
+    <row r="21" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A21" s="19"/>
+      <c r="B21" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="15">
+        <v>4</v>
+      </c>
+      <c r="E21" s="7"/>
+      <c r="F21" s="4"/>
+    </row>
+    <row r="22" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" s="15">
+        <v>2</v>
+      </c>
+      <c r="E22" s="7"/>
+      <c r="F22" s="4"/>
+    </row>
+    <row r="23" spans="1:6" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A23" s="19"/>
+      <c r="B23" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D23" s="15">
+        <v>2</v>
+      </c>
+      <c r="E23" s="7"/>
+      <c r="F23" s="4"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="4"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="2"/>
+      <c r="B27" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="3"/>
-    </row>
-    <row r="3" spans="1:4" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="8"/>
-      <c r="D3" s="3"/>
-    </row>
-    <row r="4" spans="1:4" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
-      <c r="B4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="8"/>
-      <c r="D4" s="3"/>
-    </row>
-    <row r="5" spans="1:4" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="1"/>
-      <c r="B5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="3"/>
-    </row>
-    <row r="6" spans="1:4" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="11"/>
-      <c r="B6" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="8" t="s">
+      <c r="C27" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D27" s="3"/>
+      <c r="F27" s="4"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="3"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="11"/>
-      <c r="B7" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="3"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="8"/>
-      <c r="D8" s="3"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="11"/>
-      <c r="B9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="8"/>
-      <c r="D9" s="3"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="11"/>
-      <c r="B10" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="8"/>
-      <c r="D10" s="3"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="14"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="10"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
+      <c r="C28" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D28" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="2">
